--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T08:19:30+00:00</t>
+          <t>2026-06-09T10:57:51+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T10:57:51+00:00</t>
+          <t>2026-06-09T16:55:06+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:06+00:00</t>
+          <t>2026-06-09T19:08:16+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T19:08:16+00:00</t>
+          <t>2026-06-09T19:50:55+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T19:50:55+00:00</t>
+          <t>2026-06-09T20:50:31+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T20:50:31+00:00</t>
+          <t>2026-06-09T21:53:55+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:06+00:00</t>
+          <t>2026-06-09T22:25:17+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T22:25:17+00:00</t>
+          <t>2026-06-09T23:12:23+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:23+00:00</t>
+          <t>2026-06-09T23:31:16+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:31:16+00:00</t>
+          <t>2026-06-10T01:08:53+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T01:08:53+00:00</t>
+          <t>2026-06-10T01:48:56+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T01:48:56+00:00</t>
+          <t>2026-06-10T05:56:09+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T05:56:09+00:00</t>
+          <t>2026-06-10T07:53:50+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T07:53:50+00:00</t>
+          <t>2026-06-10T10:52:03+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:23+00:00</t>
+          <t>2026-06-10T10:52:03+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
+++ b/settlements/obex/2026-02/obex_settlement_february_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:03+00:00</t>
+          <t>2026-07-03T07:03:00+00:00</t>
         </is>
       </c>
     </row>
